--- a/public/files/product.xlsx
+++ b/public/files/product.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ilham\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ilham\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE508424-D22A-4BB4-8910-C6D9C5240320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63878C14-3113-4CF8-BDBE-222A5276D138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9FD10F62-A4D3-4E41-8FB5-585179A01A00}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>product_name</t>
   </si>
@@ -58,6 +58,12 @@
   </si>
   <si>
     <t>variant_img</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>discount_price</t>
   </si>
 </sst>
 </file>
@@ -420,10 +426,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB08E43-2100-4D0B-994E-68D8015C5684}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -447,6 +453,12 @@
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/public/files/product.xlsx
+++ b/public/files/product.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ilham\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63878C14-3113-4CF8-BDBE-222A5276D138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15BE0D8D-6E9D-4634-BBCD-8AE14C1E995D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9FD10F62-A4D3-4E41-8FB5-585179A01A00}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>product_name</t>
   </si>
@@ -64,6 +64,12 @@
   </si>
   <si>
     <t>discount_price</t>
+  </si>
+  <si>
+    <t>stock</t>
+  </si>
+  <si>
+    <t>note</t>
   </si>
 </sst>
 </file>
@@ -426,10 +432,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB08E43-2100-4D0B-994E-68D8015C5684}">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -459,6 +465,12 @@
       </c>
       <c r="J1" s="1" t="s">
         <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/public/files/product.xlsx
+++ b/public/files/product.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ilham\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ilham\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15BE0D8D-6E9D-4634-BBCD-8AE14C1E995D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B221041-524F-49F7-B8E2-6D13BC602F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9FD10F62-A4D3-4E41-8FB5-585179A01A00}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>product_name</t>
   </si>
@@ -70,6 +70,9 @@
   </si>
   <si>
     <t>note</t>
+  </si>
+  <si>
+    <t>product_code</t>
   </si>
 </sst>
 </file>
@@ -113,10 +116,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -432,48 +438,127 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB08E43-2100-4D0B-994E-68D8015C5684}">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/files/product.xlsx
+++ b/public/files/product.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ilham\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B221041-524F-49F7-B8E2-6D13BC602F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{327B0C08-A84A-4F81-BDE5-8F8171D566D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9FD10F62-A4D3-4E41-8FB5-585179A01A00}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>product_name</t>
   </si>
@@ -67,9 +67,6 @@
   </si>
   <si>
     <t>stock</t>
-  </si>
-  <si>
-    <t>note</t>
   </si>
   <si>
     <t>product_code</t>
@@ -443,7 +440,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -478,9 +475,7 @@
       <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>

--- a/public/files/product.xlsx
+++ b/public/files/product.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ilham\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{327B0C08-A84A-4F81-BDE5-8F8171D566D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E4A704-44C2-474E-8A3C-FD04DA1D94CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9FD10F62-A4D3-4E41-8FB5-585179A01A00}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>product_name</t>
   </si>
@@ -61,9 +61,6 @@
   </si>
   <si>
     <t>price</t>
-  </si>
-  <si>
-    <t>discount_price</t>
   </si>
   <si>
     <t>stock</t>
@@ -435,12 +432,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB08E43-2100-4D0B-994E-68D8015C5684}">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -472,12 +469,9 @@
       <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1"/>
+      <c r="L1" s="1"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -490,9 +484,8 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -505,9 +498,8 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -520,9 +512,8 @@
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -535,9 +526,8 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -550,7 +540,6 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/files/product.xlsx
+++ b/public/files/product.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ilham\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ilham\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E4A704-44C2-474E-8A3C-FD04DA1D94CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F8F596E-F90E-4479-BEC2-7359723D00FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9FD10F62-A4D3-4E41-8FB5-585179A01A00}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>product_name</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>product_code</t>
+  </si>
+  <si>
+    <t>status</t>
   </si>
 </sst>
 </file>
@@ -432,10 +435,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB08E43-2100-4D0B-994E-68D8015C5684}">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -443,35 +446,38 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -485,7 +491,7 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -499,7 +505,7 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -513,7 +519,7 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -527,7 +533,7 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
